--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="163">
   <si>
     <t>#</t>
   </si>
@@ -1661,7 +1661,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>666</v>
+        <v>888</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>199800</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1697,7 +1697,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>666</v>
+        <v>888</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>199800</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1733,7 +1733,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>666</v>
+        <v>888</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>199800</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -3673,12 +3673,6 @@
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A63" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C63" s="1">
         <v>68</v>
       </c>
@@ -3715,12 +3709,6 @@
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C64" s="1">
         <v>69</v>
       </c>
